--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8347,0.0255,0.1951,0.0039</t>
-  </si>
-  <si>
-    <t>0.8785,0.0319,0.1234,0.0082</t>
-  </si>
-  <si>
-    <t>0.8878,0.0287,0.0952,0.0123</t>
-  </si>
-  <si>
-    <t>0.9070,0.0240,0.0705,0.0080</t>
-  </si>
-  <si>
-    <t>0.8654,0.0967,0.0403,0.0093</t>
-  </si>
-  <si>
-    <t>0.9188,0.0483,0.0211,0.0038</t>
-  </si>
-  <si>
-    <t>0.9276,0.0487,0.0236,0.0026</t>
-  </si>
-  <si>
-    <t>0.8186,0.1548,0.0409,0.0048</t>
-  </si>
-  <si>
-    <t>0.7883,0.1317,0.0800,0.0117</t>
-  </si>
-  <si>
-    <t>0.8077,0.1577,0.0476,0.0075</t>
-  </si>
-  <si>
-    <t>0.8955,0.0473,0.0344,0.0153</t>
-  </si>
-  <si>
-    <t>0.8004,0.1430,0.0788,0.0140</t>
-  </si>
-  <si>
-    <t>0.9154,0.0283,0.0619,0.0014</t>
-  </si>
-  <si>
-    <t>0.9204,0.0224,0.0649,0.0014</t>
-  </si>
-  <si>
-    <t>0.8106,0.0929,0.1146,0.0054</t>
-  </si>
-  <si>
-    <t>0.8422,0.0352,0.1672,0.0020</t>
-  </si>
-  <si>
-    <t>0.9268,0.0088,0.0924,0.0018</t>
-  </si>
-  <si>
-    <t>0.3727,0.6223,0.0746,0.0026</t>
-  </si>
-  <si>
-    <t>0.2104,0.7784,0.0784,0.0054</t>
-  </si>
-  <si>
-    <t>0.3999,0.6039,0.1021,0.0057</t>
-  </si>
-  <si>
-    <t>0.3254,0.7404,0.0316,0.0011</t>
-  </si>
-  <si>
-    <t>0.0693,0.9443,0.0222,0.0011</t>
-  </si>
-  <si>
-    <t>0.7808,0.0325,0.3159,0.0043</t>
-  </si>
-  <si>
-    <t>0.8130,0.0679,0.1358,0.0036</t>
-  </si>
-  <si>
-    <t>0.8781,0.0110,0.1990,0.0009</t>
-  </si>
-  <si>
-    <t>0.9277,0.0170,0.0634,0.0006</t>
-  </si>
-  <si>
-    <t>0.9405,0.0058,0.1165,0.0012</t>
-  </si>
-  <si>
-    <t>0.7996,0.0525,0.1904,0.0049</t>
-  </si>
-  <si>
-    <t>0.7648,0.0071,0.4646,0.0021</t>
-  </si>
-  <si>
-    <t>0.8378,0.1633,0.0185,0.0004</t>
-  </si>
-  <si>
-    <t>0.8658,0.0563,0.0641,0.0019</t>
-  </si>
-  <si>
-    <t>0.0501,0.4576,0.8562,0.0051</t>
-  </si>
-  <si>
-    <t>0.6207,0.3231,0.0953,0.0040</t>
-  </si>
-  <si>
-    <t>0.7381,0.2077,0.0574,0.0042</t>
-  </si>
-  <si>
-    <t>0.8886,0.0803,0.0385,0.0017</t>
-  </si>
-  <si>
-    <t>0.4484,0.5813,0.0785,0.0060</t>
-  </si>
-  <si>
-    <t>0.4116,0.4564,0.2269,0.0054</t>
-  </si>
-  <si>
-    <t>0.4074,0.3355,0.4112,0.0036</t>
-  </si>
-  <si>
-    <t>0.8635,0.0244,0.1870,0.0103</t>
-  </si>
-  <si>
-    <t>0.5868,0.2116,0.3039,0.0035</t>
-  </si>
-  <si>
-    <t>0.8157,0.0711,0.1384,0.0041</t>
-  </si>
-  <si>
-    <t>0.7774,0.0433,0.2127,0.0014</t>
-  </si>
-  <si>
-    <t>0.4407,0.3063,0.2855,0.0028</t>
-  </si>
-  <si>
-    <t>0.6038,0.0920,0.3517,0.0022</t>
-  </si>
-  <si>
-    <t>0.9443,0.0201,0.0348,0.0009</t>
-  </si>
-  <si>
-    <t>0.4919,0.5324,0.0439,0.0023</t>
-  </si>
-  <si>
-    <t>0.4474,0.5632,0.0690,0.0014</t>
-  </si>
-  <si>
-    <t>0.1545,0.8555,0.0925,0.0024</t>
-  </si>
-  <si>
-    <t>0.1318,0.3457,0.7499,0.0029</t>
-  </si>
-  <si>
-    <t>0.2527,0.3416,0.5943,0.0038</t>
-  </si>
-  <si>
-    <t>0.8962,0.0314,0.1005,0.0022</t>
-  </si>
-  <si>
-    <t>0.7109,0.0602,0.3147,0.0039</t>
-  </si>
-  <si>
-    <t>0.4840,0.0750,0.5440,0.0039</t>
-  </si>
-  <si>
-    <t>0.7988,0.0528,0.1537,0.0011</t>
-  </si>
-  <si>
-    <t>0.7903,0.1592,0.0808,0.0102</t>
-  </si>
-  <si>
-    <t>0.7735,0.2019,0.0587,0.0086</t>
-  </si>
-  <si>
-    <t>0.6522,0.3663,0.0529,0.0100</t>
-  </si>
-  <si>
-    <t>0.1205,0.6961,0.5789,0.0119</t>
-  </si>
-  <si>
-    <t>0.8979,0.0557,0.0381,0.0097</t>
-  </si>
-  <si>
-    <t>0.8519,0.0739,0.0841,0.0257</t>
-  </si>
-  <si>
-    <t>0.7845,0.1973,0.0358,0.0038</t>
-  </si>
-  <si>
-    <t>0.0332,0.6429,0.8761,0.0008</t>
-  </si>
-  <si>
-    <t>0.1685,0.3769,0.6424,0.0015</t>
-  </si>
-  <si>
-    <t>0.3005,0.3568,0.4956,0.0073</t>
-  </si>
-  <si>
-    <t>0.1315,0.6023,0.5951,0.0018</t>
-  </si>
-  <si>
-    <t>0.0598,0.4374,0.8199,0.0024</t>
-  </si>
-  <si>
-    <t>0.4482,0.6066,0.0494,0.0014</t>
-  </si>
-  <si>
-    <t>0.0532,0.9660,0.0096,0.0001</t>
-  </si>
-  <si>
-    <t>0.8885,0.0457,0.0644,0.0018</t>
-  </si>
-  <si>
-    <t>0.8609,0.0932,0.0357,0.0024</t>
-  </si>
-  <si>
-    <t>0.0690,0.6649,0.5877,0.0028</t>
-  </si>
-  <si>
-    <t>0.0688,0.8624,0.3899,0.0024</t>
-  </si>
-  <si>
-    <t>0.2647,0.4100,0.5357,0.0028</t>
-  </si>
-  <si>
-    <t>0.0531,0.8547,0.5125,0.0032</t>
-  </si>
-  <si>
-    <t>0.1060,0.7525,0.4973,0.0021</t>
-  </si>
-  <si>
-    <t>0.8694,0.0313,0.1448,0.0035</t>
-  </si>
-  <si>
-    <t>0.8179,0.0705,0.1281,0.0247</t>
-  </si>
-  <si>
-    <t>0.8963,0.0226,0.1160,0.0072</t>
-  </si>
-  <si>
-    <t>0.8946,0.0193,0.1512,0.0026</t>
-  </si>
-  <si>
-    <t>0.8720,0.0269,0.1203,0.0028</t>
-  </si>
-  <si>
-    <t>0.8096,0.0720,0.1229,0.0134</t>
-  </si>
-  <si>
-    <t>0.0739,0.7005,0.6472,0.0021</t>
-  </si>
-  <si>
-    <t>0.0700,0.5558,0.7979,0.0036</t>
-  </si>
-  <si>
-    <t>0.4190,0.1871,0.4909,0.0037</t>
-  </si>
-  <si>
-    <t>0.2769,0.5010,0.4461,0.0054</t>
-  </si>
-  <si>
-    <t>0.0105,0.9128,0.7897,0.0008</t>
-  </si>
-  <si>
-    <t>0.0300,0.9059,0.5956,0.0035</t>
-  </si>
-  <si>
-    <t>0.8106,0.1285,0.0823,0.0133</t>
-  </si>
-  <si>
-    <t>0.8067,0.1768,0.0332,0.0075</t>
-  </si>
-  <si>
-    <t>0.5607,0.4193,0.0848,0.0158</t>
-  </si>
-  <si>
-    <t>0.7863,0.1718,0.0496,0.0154</t>
-  </si>
-  <si>
-    <t>0.8636,0.0701,0.0684,0.0174</t>
-  </si>
-  <si>
-    <t>0.8129,0.1277,0.0556,0.0170</t>
-  </si>
-  <si>
-    <t>0.8291,0.1718,0.0307,0.0041</t>
-  </si>
-  <si>
-    <t>0.8252,0.1495,0.0602,0.0100</t>
-  </si>
-  <si>
-    <t>0.8411,0.1267,0.0507,0.0042</t>
-  </si>
-  <si>
-    <t>0.8631,0.0755,0.0771,0.0066</t>
-  </si>
-  <si>
-    <t>0.9061,0.0505,0.0307,0.0084</t>
-  </si>
-  <si>
-    <t>0.8687,0.0759,0.0379,0.0102</t>
-  </si>
-  <si>
-    <t>0.8299,0.0977,0.0490,0.0225</t>
-  </si>
-  <si>
-    <t>0.8435,0.1303,0.0459,0.0034</t>
-  </si>
-  <si>
-    <t>0.8041,0.1828,0.0283,0.0070</t>
-  </si>
-  <si>
-    <t>0.8187,0.0926,0.0802,0.0286</t>
-  </si>
-  <si>
-    <t>0.7092,0.0240,0.4388,0.0021</t>
-  </si>
-  <si>
-    <t>0.3781,0.3042,0.2219,0.0011</t>
-  </si>
-  <si>
-    <t>0.9594,0.0053,0.0612,0.0006</t>
-  </si>
-  <si>
-    <t>0.8875,0.0583,0.0476,0.0014</t>
-  </si>
-  <si>
-    <t>0.0531,0.9479,0.0224,0.0032</t>
-  </si>
-  <si>
-    <t>0.2505,0.7754,0.0592,0.0050</t>
-  </si>
-  <si>
-    <t>0.6972,0.2518,0.0622,0.0053</t>
-  </si>
-  <si>
-    <t>0.2958,0.7607,0.0334,0.0016</t>
-  </si>
-  <si>
-    <t>0.1794,0.8408,0.0539,0.0068</t>
-  </si>
-  <si>
-    <t>0.1362,0.8789,0.0189,0.0009</t>
-  </si>
-  <si>
-    <t>0.7948,0.1865,0.0390,0.0034</t>
-  </si>
-  <si>
-    <t>0.8137,0.0914,0.1051,0.0059</t>
-  </si>
-  <si>
-    <t>0.8830,0.0242,0.1354,0.0017</t>
-  </si>
-  <si>
-    <t>0.6649,0.1527,0.2053,0.0055</t>
-  </si>
-  <si>
-    <t>0.9627,0.0066,0.0411,0.0009</t>
-  </si>
-  <si>
-    <t>0.9276,0.0382,0.0303,0.0009</t>
-  </si>
-  <si>
-    <t>0.4669,0.5480,0.0505,0.0007</t>
-  </si>
-  <si>
-    <t>0.1370,0.8679,0.1121,0.0070</t>
-  </si>
-  <si>
-    <t>0.8512,0.0611,0.1023,0.0055</t>
-  </si>
-  <si>
-    <t>0.1458,0.8394,0.0874,0.0008</t>
-  </si>
-  <si>
-    <t>0.2362,0.8048,0.0522,0.0030</t>
-  </si>
-  <si>
-    <t>0.8716,0.1177,0.0229,0.0010</t>
-  </si>
-  <si>
-    <t>0.6371,0.3429,0.0502,0.0050</t>
-  </si>
-  <si>
-    <t>0.9076,0.0537,0.0586,0.0046</t>
-  </si>
-  <si>
-    <t>0.8969,0.0375,0.0673,0.0081</t>
-  </si>
-  <si>
-    <t>0.8645,0.0769,0.0532,0.0118</t>
-  </si>
-  <si>
-    <t>0.8393,0.0948,0.0594,0.0073</t>
-  </si>
-  <si>
-    <t>0.9143,0.0716,0.0255,0.0026</t>
-  </si>
-  <si>
-    <t>0.9633,0.0180,0.0196,0.0008</t>
-  </si>
-  <si>
-    <t>0.8105,0.1465,0.0503,0.0080</t>
-  </si>
-  <si>
-    <t>0.7580,0.2550,0.0342,0.0032</t>
-  </si>
-  <si>
-    <t>0.3227,0.3480,0.4603,0.0033</t>
-  </si>
-  <si>
-    <t>0.2858,0.5567,0.2517,0.0012</t>
-  </si>
-  <si>
-    <t>0.3842,0.2683,0.4301,0.0040</t>
-  </si>
-  <si>
-    <t>0.3466,0.4543,0.3338,0.0051</t>
-  </si>
-  <si>
-    <t>0.9521,0.0103,0.0550,0.0010</t>
-  </si>
-  <si>
-    <t>0.8655,0.0395,0.1101,0.0026</t>
-  </si>
-  <si>
-    <t>0.8556,0.0572,0.1062,0.0026</t>
-  </si>
-  <si>
-    <t>0.8725,0.0458,0.0912,0.0045</t>
-  </si>
-  <si>
-    <t>0.8467,0.0476,0.1350,0.0057</t>
-  </si>
-  <si>
-    <t>0.8556,0.0088,0.1662,0.0152</t>
-  </si>
-  <si>
-    <t>0.8494,0.0400,0.1203,0.0284</t>
-  </si>
-  <si>
-    <t>0.8804,0.0105,0.1085,0.0201</t>
-  </si>
-  <si>
-    <t>0.1246,0.6037,0.6307,0.0040</t>
-  </si>
-  <si>
-    <t>0.6446,0.3350,0.0830,0.0163</t>
-  </si>
-  <si>
-    <t>0.8067,0.0979,0.1445,0.0139</t>
-  </si>
-  <si>
-    <t>0.8512,0.1004,0.0448,0.0113</t>
-  </si>
-  <si>
-    <t>0.7531,0.2432,0.0619,0.0054</t>
-  </si>
-  <si>
-    <t>0.8548,0.0605,0.0934,0.0077</t>
-  </si>
-  <si>
-    <t>0.9554,0.0082,0.0361,0.0029</t>
-  </si>
-  <si>
-    <t>0.7958,0.1418,0.0514,0.0129</t>
-  </si>
-  <si>
-    <t>0.1411,0.5064,0.6652,0.0089</t>
-  </si>
-  <si>
-    <t>0.8406,0.1376,0.0330,0.0032</t>
-  </si>
-  <si>
-    <t>0.8283,0.0502,0.1427,0.0065</t>
-  </si>
-  <si>
-    <t>0.6630,0.3032,0.0663,0.0064</t>
-  </si>
-  <si>
-    <t>0.7820,0.1396,0.0988,0.0093</t>
-  </si>
-  <si>
-    <t>0.8834,0.0429,0.0848,0.0025</t>
-  </si>
-  <si>
-    <t>0.4958,0.4837,0.0782,0.0047</t>
-  </si>
-  <si>
-    <t>0.7946,0.1606,0.0489,0.0021</t>
-  </si>
-  <si>
-    <t>0.9021,0.0582,0.0419,0.0021</t>
-  </si>
-  <si>
-    <t>0.7617,0.2081,0.0707,0.0076</t>
-  </si>
-  <si>
-    <t>0.8036,0.2007,0.0197,0.0017</t>
-  </si>
-  <si>
-    <t>0.9065,0.0462,0.0409,0.0047</t>
-  </si>
-  <si>
-    <t>0.8985,0.0535,0.0296,0.0118</t>
-  </si>
-  <si>
-    <t>0.7264,0.2133,0.0764,0.0087</t>
-  </si>
-  <si>
-    <t>0.7633,0.2358,0.0494,0.0049</t>
-  </si>
-  <si>
-    <t>0.7985,0.1686,0.0649,0.0100</t>
-  </si>
-  <si>
-    <t>0.9163,0.0550,0.0207,0.0058</t>
-  </si>
-  <si>
-    <t>0.5333,0.5082,0.0705,0.0038</t>
-  </si>
-  <si>
-    <t>0.4498,0.5417,0.1000,0.0075</t>
-  </si>
-  <si>
-    <t>0.5579,0.3485,0.0924,0.0046</t>
-  </si>
-  <si>
-    <t>0.9053,0.0497,0.0262,0.0070</t>
-  </si>
-  <si>
-    <t>0.6215,0.4329,0.0416,0.0025</t>
-  </si>
-  <si>
-    <t>0.7339,0.2137,0.0514,0.0128</t>
-  </si>
-  <si>
-    <t>0.8141,0.1510,0.0481,0.0026</t>
-  </si>
-  <si>
-    <t>0.8586,0.1234,0.0311,0.0029</t>
-  </si>
-  <si>
-    <t>0.0015,0.8788,0.9477,0.0004</t>
-  </si>
-  <si>
-    <t>0.4628,0.4997,0.1064,0.0062</t>
-  </si>
-  <si>
-    <t>0.3821,0.0452,0.6490,0.0012</t>
-  </si>
-  <si>
-    <t>0.6904,0.1457,0.1784,0.0046</t>
-  </si>
-  <si>
-    <t>0.8535,0.0526,0.1041,0.0030</t>
-  </si>
-  <si>
-    <t>0.7078,0.1184,0.2259,0.0023</t>
-  </si>
-  <si>
-    <t>0.5396,0.2953,0.1409,0.0019</t>
-  </si>
-  <si>
-    <t>0.2435,0.1604,0.6063,0.0012</t>
-  </si>
-  <si>
-    <t>0.4276,0.3722,0.1906,0.0019</t>
-  </si>
-  <si>
-    <t>0.7204,0.1545,0.1291,0.0046</t>
-  </si>
-  <si>
-    <t>0.8072,0.0452,0.1429,0.0013</t>
-  </si>
-  <si>
-    <t>0.7801,0.1199,0.0980,0.0079</t>
-  </si>
-  <si>
-    <t>0.9083,0.0265,0.0676,0.0006</t>
-  </si>
-  <si>
-    <t>0.6887,0.2051,0.1048,0.0025</t>
-  </si>
-  <si>
-    <t>0.5475,0.3182,0.1273,0.0051</t>
-  </si>
-  <si>
-    <t>0.7716,0.1034,0.1514,0.0110</t>
-  </si>
-  <si>
-    <t>0.8204,0.0574,0.1168,0.0036</t>
-  </si>
-  <si>
-    <t>0.7333,0.2007,0.0710,0.0079</t>
-  </si>
-  <si>
-    <t>0.7410,0.2538,0.0354,0.0051</t>
-  </si>
-  <si>
-    <t>0.8090,0.1705,0.0355,0.0016</t>
-  </si>
-  <si>
-    <t>0.7110,0.2729,0.0664,0.0072</t>
-  </si>
-  <si>
-    <t>0.6238,0.3640,0.0889,0.0155</t>
-  </si>
-  <si>
-    <t>0.7016,0.2056,0.0744,0.0029</t>
-  </si>
-  <si>
-    <t>0.6074,0.2793,0.1612,0.0143</t>
-  </si>
-  <si>
-    <t>0.9190,0.0097,0.1001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9380,0.0137,0.0726,0.0010</t>
-  </si>
-  <si>
-    <t>0.8851,0.0450,0.0825,0.0056</t>
-  </si>
-  <si>
-    <t>0.5336,0.1600,0.2969,0.0054</t>
-  </si>
-  <si>
-    <t>0.3772,0.3623,0.3863,0.0040</t>
-  </si>
-  <si>
-    <t>0.6699,0.1570,0.2293,0.0073</t>
-  </si>
-  <si>
-    <t>0.5349,0.1355,0.3895,0.0022</t>
-  </si>
-  <si>
-    <t>0.5099,0.2441,0.3800,0.0137</t>
-  </si>
-  <si>
-    <t>0.8427,0.1389,0.0281,0.0098</t>
-  </si>
-  <si>
-    <t>0.8950,0.0557,0.0520,0.0055</t>
-  </si>
-  <si>
-    <t>0.7426,0.2136,0.0615,0.0097</t>
-  </si>
-  <si>
-    <t>0.7385,0.2683,0.0330,0.0047</t>
-  </si>
-  <si>
-    <t>0.8217,0.1331,0.0494,0.0107</t>
-  </si>
-  <si>
-    <t>0.7954,0.1580,0.0586,0.0100</t>
-  </si>
-  <si>
-    <t>0.7251,0.2407,0.0813,0.0073</t>
-  </si>
-  <si>
-    <t>0.8263,0.1268,0.0572,0.0076</t>
-  </si>
-  <si>
-    <t>0.8590,0.0503,0.0899,0.0048</t>
-  </si>
-  <si>
-    <t>0.9188,0.0435,0.0408,0.0020</t>
-  </si>
-  <si>
-    <t>0.6216,0.1926,0.2461,0.0158</t>
-  </si>
-  <si>
-    <t>0.7323,0.0450,0.2564,0.0020</t>
-  </si>
-  <si>
-    <t>0.5248,0.3177,0.2451,0.0141</t>
-  </si>
-  <si>
-    <t>0.3967,0.1275,0.4049,0.0006</t>
-  </si>
-  <si>
-    <t>0.4535,0.0610,0.5960,0.0010</t>
-  </si>
-  <si>
-    <t>0.8376,0.0335,0.1677,0.0023</t>
-  </si>
-  <si>
-    <t>0.0319,0.1941,0.9687,0.0003</t>
-  </si>
-  <si>
-    <t>0.4287,0.2981,0.3090,0.0053</t>
-  </si>
-  <si>
-    <t>0.6794,0.1710,0.1095,0.0022</t>
-  </si>
-  <si>
-    <t>0.8787,0.0400,0.0837,0.0042</t>
-  </si>
-  <si>
-    <t>0.9213,0.0074,0.1448,0.0012</t>
-  </si>
-  <si>
-    <t>0.8850,0.0510,0.0721,0.0048</t>
-  </si>
-  <si>
-    <t>0.8268,0.0942,0.0817,0.0110</t>
-  </si>
-  <si>
-    <t>0.8296,0.1239,0.0525,0.0067</t>
-  </si>
-  <si>
-    <t>0.8170,0.1366,0.0538,0.0079</t>
-  </si>
-  <si>
-    <t>0.7806,0.1787,0.0647,0.0217</t>
-  </si>
-  <si>
-    <t>0.6522,0.2720,0.1055,0.0382</t>
-  </si>
-  <si>
-    <t>0.6497,0.3196,0.0899,0.0132</t>
-  </si>
-  <si>
-    <t>0.7272,0.2417,0.0701,0.0090</t>
-  </si>
-  <si>
-    <t>0.7829,0.1835,0.0509,0.0104</t>
-  </si>
-  <si>
-    <t>0.6367,0.1926,0.1491,0.0020</t>
-  </si>
-  <si>
-    <t>0.0509,0.4473,0.7753,0.0006</t>
-  </si>
-  <si>
-    <t>0.3783,0.3178,0.2994,0.0023</t>
-  </si>
-  <si>
-    <t>0.8868,0.0167,0.1485,0.0009</t>
-  </si>
-  <si>
-    <t>0.4788,0.1843,0.3253,0.0016</t>
-  </si>
-  <si>
-    <t>0.8768,0.0343,0.1146,0.0035</t>
-  </si>
-  <si>
-    <t>0.7417,0.0684,0.2191,0.0042</t>
-  </si>
-  <si>
-    <t>0.4939,0.2461,0.3994,0.0226</t>
-  </si>
-  <si>
-    <t>0.9289,0.0165,0.0545,0.0038</t>
-  </si>
-  <si>
-    <t>0.8558,0.0412,0.1395,0.0073</t>
-  </si>
-  <si>
-    <t>0.8758,0.0324,0.1295,0.0073</t>
-  </si>
-  <si>
-    <t>0.8963,0.0166,0.1215,0.0042</t>
-  </si>
-  <si>
-    <t>0.8600,0.0228,0.1515,0.0176</t>
-  </si>
-  <si>
-    <t>0.9235,0.0244,0.0626,0.0027</t>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.9287,0.0510,0.0133,0.0131</t>
+  </si>
+  <si>
+    <t>0.0530,0.0068,0.0032,0.9678</t>
+  </si>
+  <si>
+    <t>0.4540,0.0118,0.0174,0.6206</t>
+  </si>
+  <si>
+    <t>0.0787,0.0034,0.0116,0.9478</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9915,0.0028,0.0011,0.0023</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9934,0.0023,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9875,0.0073,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.9922,0.0057,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0010,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9906,0.0035,0.0020,0.0022</t>
+  </si>
+  <si>
+    <t>0.8064,0.0129,0.2602,0.0077</t>
+  </si>
+  <si>
+    <t>0.0649,0.0163,0.9196,0.0040</t>
+  </si>
+  <si>
+    <t>0.5415,0.0110,0.5994,0.0006</t>
+  </si>
+  <si>
+    <t>0.0273,0.5293,0.6293,0.0093</t>
+  </si>
+  <si>
+    <t>0.5348,0.0305,0.5138,0.0087</t>
+  </si>
+  <si>
+    <t>0.0018,0.9957,0.0021,0.0035</t>
+  </si>
+  <si>
+    <t>0.0032,0.9928,0.0068,0.0011</t>
+  </si>
+  <si>
+    <t>0.1396,0.8997,0.0044,0.0017</t>
+  </si>
+  <si>
+    <t>0.0078,0.9888,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.0014,0.9969,0.0041,0.0006</t>
+  </si>
+  <si>
+    <t>0.6181,0.0443,0.4223,0.0298</t>
+  </si>
+  <si>
+    <t>0.1146,0.1768,0.7435,0.0657</t>
+  </si>
+  <si>
+    <t>0.0020,0.0106,0.9838,0.0127</t>
+  </si>
+  <si>
+    <t>0.0496,0.0098,0.9234,0.0162</t>
+  </si>
+  <si>
+    <t>0.0170,0.0043,0.9788,0.0026</t>
+  </si>
+  <si>
+    <t>0.1449,0.0210,0.8285,0.0283</t>
+  </si>
+  <si>
+    <t>0.0038,0.0011,0.9919,0.0042</t>
+  </si>
+  <si>
+    <t>0.1489,0.8738,0.0128,0.0008</t>
+  </si>
+  <si>
+    <t>0.4505,0.4925,0.1388,0.0264</t>
+  </si>
+  <si>
+    <t>0.0044,0.0086,0.9872,0.0100</t>
+  </si>
+  <si>
+    <t>0.0069,0.7521,0.6447,0.0009</t>
+  </si>
+  <si>
+    <t>0.7940,0.1412,0.0705,0.0271</t>
+  </si>
+  <si>
+    <t>0.9326,0.0198,0.0424,0.0017</t>
+  </si>
+  <si>
+    <t>0.5399,0.5024,0.0136,0.0006</t>
+  </si>
+  <si>
+    <t>0.0045,0.9441,0.7885,0.0008</t>
+  </si>
+  <si>
+    <t>0.0104,0.3887,0.8984,0.0047</t>
+  </si>
+  <si>
+    <t>0.1470,0.0355,0.8736,0.0107</t>
+  </si>
+  <si>
+    <t>0.0520,0.3000,0.8656,0.0061</t>
+  </si>
+  <si>
+    <t>0.1262,0.0111,0.6464,0.1916</t>
+  </si>
+  <si>
+    <t>0.0121,0.1556,0.9652,0.0031</t>
+  </si>
+  <si>
+    <t>0.0059,0.9657,0.0393,0.0010</t>
+  </si>
+  <si>
+    <t>0.0055,0.0307,0.9850,0.0014</t>
+  </si>
+  <si>
+    <t>0.1507,0.6344,0.2669,0.1770</t>
+  </si>
+  <si>
+    <t>0.0008,0.9945,0.0144,0.0073</t>
+  </si>
+  <si>
+    <t>0.0018,0.9895,0.0466,0.0014</t>
+  </si>
+  <si>
+    <t>0.0007,0.9942,0.0759,0.0005</t>
+  </si>
+  <si>
+    <t>0.0029,0.2343,0.9780,0.0048</t>
+  </si>
+  <si>
+    <t>0.0022,0.2072,0.9884,0.0013</t>
+  </si>
+  <si>
+    <t>0.0294,0.0100,0.9542,0.0079</t>
+  </si>
+  <si>
+    <t>0.0564,0.0250,0.9170,0.0141</t>
+  </si>
+  <si>
+    <t>0.0290,0.0842,0.9535,0.0044</t>
+  </si>
+  <si>
+    <t>0.0112,0.0643,0.9695,0.0042</t>
+  </si>
+  <si>
+    <t>0.9160,0.1211,0.0062,0.0015</t>
+  </si>
+  <si>
+    <t>0.9837,0.0053,0.0129,0.0011</t>
+  </si>
+  <si>
+    <t>0.9631,0.0205,0.0095,0.0099</t>
+  </si>
+  <si>
+    <t>0.0080,0.0664,0.9796,0.0065</t>
+  </si>
+  <si>
+    <t>0.9783,0.0159,0.0083,0.0017</t>
+  </si>
+  <si>
+    <t>0.9931,0.0030,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9713,0.0432,0.0033,0.0008</t>
+  </si>
+  <si>
+    <t>0.0016,0.9230,0.9247,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.4269,0.9896,0.0007</t>
+  </si>
+  <si>
+    <t>0.0068,0.0520,0.9591,0.0116</t>
+  </si>
+  <si>
+    <t>0.0008,0.9615,0.7704,0.0002</t>
+  </si>
+  <si>
+    <t>0.0051,0.0108,0.9833,0.0058</t>
+  </si>
+  <si>
+    <t>0.0389,0.9054,0.1052,0.0034</t>
+  </si>
+  <si>
+    <t>0.0128,0.9910,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9226,0.0294,0.0432,0.0139</t>
+  </si>
+  <si>
+    <t>0.5152,0.1197,0.4680,0.0076</t>
+  </si>
+  <si>
+    <t>0.0009,0.0206,0.9959,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.8444,0.9307,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.9087,0.8049,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9857,0.2133,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.9818,0.8278,0.0003</t>
+  </si>
+  <si>
+    <t>0.0048,0.0028,0.0334,0.9880</t>
+  </si>
+  <si>
+    <t>0.0026,0.0014,0.0014,0.9976</t>
+  </si>
+  <si>
+    <t>0.0154,0.0038,0.0006,0.9922</t>
+  </si>
+  <si>
+    <t>0.0671,0.0032,0.0114,0.9592</t>
+  </si>
+  <si>
+    <t>0.0018,0.0038,0.0050,0.9964</t>
+  </si>
+  <si>
+    <t>0.0080,0.0603,0.0047,0.9848</t>
+  </si>
+  <si>
+    <t>0.0007,0.9372,0.9464,0.0003</t>
+  </si>
+  <si>
+    <t>0.0016,0.9205,0.9265,0.0006</t>
+  </si>
+  <si>
+    <t>0.0099,0.7806,0.8084,0.0041</t>
+  </si>
+  <si>
+    <t>0.0117,0.4099,0.9391,0.0027</t>
+  </si>
+  <si>
+    <t>0.0011,0.8087,0.9506,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9381,0.7872,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9904,0.0075,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9865,0.0093,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.9916,0.0048,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9912,0.0027,0.0035,0.0017</t>
+  </si>
+  <si>
+    <t>0.9923,0.0049,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.9846,0.0108,0.0072,0.0009</t>
+  </si>
+  <si>
+    <t>0.9950,0.0023,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9964,0.0009,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9955,0.0007,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9893,0.0054,0.0031,0.0025</t>
+  </si>
+  <si>
+    <t>0.9918,0.0043,0.0041,0.0009</t>
+  </si>
+  <si>
+    <t>0.9942,0.0031,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9949,0.0022,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0123,0.0158,0.9840,0.0036</t>
+  </si>
+  <si>
+    <t>0.0408,0.0080,0.9661,0.0012</t>
+  </si>
+  <si>
+    <t>0.6625,0.0699,0.2660,0.1141</t>
+  </si>
+  <si>
+    <t>0.0192,0.0045,0.9791,0.0017</t>
+  </si>
+  <si>
+    <t>0.0459,0.9573,0.0079,0.0033</t>
+  </si>
+  <si>
+    <t>0.0110,0.9867,0.0053,0.0005</t>
+  </si>
+  <si>
+    <t>0.0367,0.9649,0.0028,0.0049</t>
+  </si>
+  <si>
+    <t>0.0879,0.9254,0.0086,0.0019</t>
+  </si>
+  <si>
+    <t>0.0026,0.9942,0.0059,0.0025</t>
+  </si>
+  <si>
+    <t>0.0052,0.9921,0.0043,0.0002</t>
+  </si>
+  <si>
+    <t>0.5325,0.6122,0.0049,0.0008</t>
+  </si>
+  <si>
+    <t>0.8769,0.0154,0.1206,0.0097</t>
+  </si>
+  <si>
+    <t>0.1404,0.0998,0.7627,0.0271</t>
+  </si>
+  <si>
+    <t>0.0974,0.4059,0.4783,0.0279</t>
+  </si>
+  <si>
+    <t>0.6670,0.0172,0.4226,0.0070</t>
+  </si>
+  <si>
+    <t>0.3126,0.4727,0.0951,0.3806</t>
+  </si>
+  <si>
+    <t>0.0021,0.9934,0.0092,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0013,0.0025</t>
+  </si>
+  <si>
+    <t>0.0008,0.9961,0.0061,0.0080</t>
+  </si>
+  <si>
+    <t>0.0003,0.9567,0.9449,0.0001</t>
+  </si>
+  <si>
+    <t>0.0334,0.9629,0.0192,0.0002</t>
+  </si>
+  <si>
+    <t>0.8464,0.1429,0.0534,0.0057</t>
+  </si>
+  <si>
+    <t>0.7800,0.2253,0.0148,0.0004</t>
+  </si>
+  <si>
+    <t>0.9584,0.0334,0.0243,0.0041</t>
+  </si>
+  <si>
+    <t>0.9910,0.0023,0.0034,0.0019</t>
+  </si>
+  <si>
+    <t>0.9900,0.0018,0.0027,0.0027</t>
+  </si>
+  <si>
+    <t>0.9550,0.0161,0.0232,0.0078</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9910,0.0078,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.9913,0.0011,0.0012,0.0039</t>
+  </si>
+  <si>
+    <t>0.9865,0.0030,0.0030,0.0040</t>
+  </si>
+  <si>
+    <t>0.0027,0.7840,0.9413,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.9173,0.9483,0.0003</t>
+  </si>
+  <si>
+    <t>0.0125,0.0992,0.9503,0.0015</t>
+  </si>
+  <si>
+    <t>0.0102,0.7782,0.8968,0.0029</t>
+  </si>
+  <si>
+    <t>0.9466,0.0213,0.0146,0.0063</t>
+  </si>
+  <si>
+    <t>0.8749,0.0376,0.0460,0.0252</t>
+  </si>
+  <si>
+    <t>0.7501,0.0014,0.5162,0.0013</t>
+  </si>
+  <si>
+    <t>0.5963,0.0550,0.3916,0.0327</t>
+  </si>
+  <si>
+    <t>0.0403,0.0065,0.0129,0.9670</t>
+  </si>
+  <si>
+    <t>0.0002,0.0072,0.0004,0.9991</t>
+  </si>
+  <si>
+    <t>0.0007,0.0026,0.0007,0.9989</t>
+  </si>
+  <si>
+    <t>0.0032,0.0006,0.0026,0.9969</t>
+  </si>
+  <si>
+    <t>0.0015,0.8969,0.7319,0.0018</t>
+  </si>
+  <si>
+    <t>0.9867,0.0071,0.0044,0.0017</t>
+  </si>
+  <si>
+    <t>0.5207,0.6292,0.0048,0.0039</t>
+  </si>
+  <si>
+    <t>0.9925,0.0037,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.3321,0.7350,0.0100,0.0018</t>
+  </si>
+  <si>
+    <t>0.9865,0.0017,0.0018,0.0056</t>
+  </si>
+  <si>
+    <t>0.1216,0.0155,0.0251,0.8957</t>
+  </si>
+  <si>
+    <t>0.9650,0.0081,0.0122,0.0124</t>
+  </si>
+  <si>
+    <t>0.0104,0.0483,0.9601,0.0349</t>
+  </si>
+  <si>
+    <t>0.5065,0.0068,0.0228,0.5426</t>
+  </si>
+  <si>
+    <t>0.6541,0.0277,0.0454,0.3326</t>
+  </si>
+  <si>
+    <t>0.3481,0.5394,0.0980,0.0052</t>
+  </si>
+  <si>
+    <t>0.8361,0.1581,0.0072,0.0159</t>
+  </si>
+  <si>
+    <t>0.9317,0.0662,0.0104,0.0013</t>
+  </si>
+  <si>
+    <t>0.3426,0.5861,0.1148,0.1270</t>
+  </si>
+  <si>
+    <t>0.6986,0.0326,0.2979,0.0041</t>
+  </si>
+  <si>
+    <t>0.9232,0.0476,0.0254,0.0041</t>
+  </si>
+  <si>
+    <t>0.9885,0.0038,0.0025,0.0024</t>
+  </si>
+  <si>
+    <t>0.9913,0.0040,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9910,0.0029,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9860,0.0039,0.0027,0.0041</t>
+  </si>
+  <si>
+    <t>0.9933,0.0029,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9921,0.0028,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.9868,0.0067,0.0018,0.0028</t>
+  </si>
+  <si>
+    <t>0.9941,0.0009,0.0004,0.0022</t>
+  </si>
+  <si>
+    <t>0.8829,0.2145,0.0023,0.0004</t>
+  </si>
+  <si>
+    <t>0.7226,0.3137,0.0218,0.0022</t>
+  </si>
+  <si>
+    <t>0.4535,0.6098,0.0134,0.0023</t>
+  </si>
+  <si>
+    <t>0.8466,0.0288,0.0509,0.1195</t>
+  </si>
+  <si>
+    <t>0.9547,0.0360,0.0134,0.0046</t>
+  </si>
+  <si>
+    <t>0.9304,0.0596,0.0131,0.0082</t>
+  </si>
+  <si>
+    <t>0.9655,0.0244,0.0133,0.0028</t>
+  </si>
+  <si>
+    <t>0.8644,0.1573,0.0123,0.0114</t>
+  </si>
+  <si>
+    <t>0.0009,0.0688,0.9951,0.0010</t>
+  </si>
+  <si>
+    <t>0.9292,0.0701,0.0114,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.1000,0.9918,0.0006</t>
+  </si>
+  <si>
+    <t>0.0084,0.4073,0.9490,0.0030</t>
+  </si>
+  <si>
+    <t>0.0205,0.0146,0.9591,0.0082</t>
+  </si>
+  <si>
+    <t>0.0349,0.2135,0.9322,0.0096</t>
+  </si>
+  <si>
+    <t>0.0010,0.0188,0.9946,0.0005</t>
+  </si>
+  <si>
+    <t>0.0032,0.0233,0.9893,0.0021</t>
+  </si>
+  <si>
+    <t>0.0188,0.1166,0.9459,0.0090</t>
+  </si>
+  <si>
+    <t>0.1827,0.0637,0.7700,0.0157</t>
+  </si>
+  <si>
+    <t>0.0877,0.0241,0.8876,0.0187</t>
+  </si>
+  <si>
+    <t>0.3032,0.1403,0.4830,0.0060</t>
+  </si>
+  <si>
+    <t>0.1036,0.0471,0.8479,0.0015</t>
+  </si>
+  <si>
+    <t>0.0606,0.2027,0.7620,0.0021</t>
+  </si>
+  <si>
+    <t>0.2274,0.1124,0.6452,0.0091</t>
+  </si>
+  <si>
+    <t>0.1583,0.4116,0.5305,0.0716</t>
+  </si>
+  <si>
+    <t>0.2590,0.0592,0.6750,0.0144</t>
+  </si>
+  <si>
+    <t>0.7757,0.2814,0.0090,0.0007</t>
+  </si>
+  <si>
+    <t>0.4924,0.6452,0.0055,0.0010</t>
+  </si>
+  <si>
+    <t>0.9583,0.0551,0.0057,0.0009</t>
+  </si>
+  <si>
+    <t>0.9718,0.0428,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.8571,0.1948,0.0155,0.0038</t>
+  </si>
+  <si>
+    <t>0.6678,0.0451,0.3502,0.0056</t>
+  </si>
+  <si>
+    <t>0.8887,0.0052,0.1506,0.0106</t>
+  </si>
+  <si>
+    <t>0.8554,0.0153,0.0251,0.0869</t>
+  </si>
+  <si>
+    <t>0.6339,0.0820,0.3502,0.0365</t>
+  </si>
+  <si>
+    <t>0.5094,0.1020,0.3176,0.1286</t>
+  </si>
+  <si>
+    <t>0.0191,0.0096,0.9605,0.0094</t>
+  </si>
+  <si>
+    <t>0.0134,0.5195,0.8710,0.0095</t>
+  </si>
+  <si>
+    <t>0.0251,0.4404,0.8773,0.0376</t>
+  </si>
+  <si>
+    <t>0.1051,0.0609,0.8799,0.0036</t>
+  </si>
+  <si>
+    <t>0.0218,0.1511,0.8906,0.0091</t>
+  </si>
+  <si>
+    <t>0.9915,0.0044,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.9898,0.0051,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9949,0.0026,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9849,0.0160,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.9881,0.0067,0.0034,0.0020</t>
+  </si>
+  <si>
+    <t>0.9947,0.0032,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0047,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9844,0.0081,0.0060,0.0027</t>
+  </si>
+  <si>
+    <t>0.0178,0.0606,0.9504,0.0080</t>
+  </si>
+  <si>
+    <t>0.0392,0.7979,0.4371,0.0050</t>
+  </si>
+  <si>
+    <t>0.9579,0.0171,0.0193,0.0026</t>
+  </si>
+  <si>
+    <t>0.0004,0.0026,0.9972,0.0013</t>
+  </si>
+  <si>
+    <t>0.0025,0.0221,0.9851,0.0103</t>
+  </si>
+  <si>
+    <t>0.0016,0.4062,0.9731,0.0012</t>
+  </si>
+  <si>
+    <t>0.0029,0.0077,0.9944,0.0013</t>
+  </si>
+  <si>
+    <t>0.0220,0.1576,0.9286,0.0059</t>
+  </si>
+  <si>
+    <t>0.0007,0.0060,0.9974,0.0015</t>
+  </si>
+  <si>
+    <t>0.0253,0.0898,0.9267,0.0260</t>
+  </si>
+  <si>
+    <t>0.0238,0.0845,0.9023,0.0164</t>
+  </si>
+  <si>
+    <t>0.7417,0.0254,0.3368,0.0192</t>
+  </si>
+  <si>
+    <t>0.5049,0.0021,0.6714,0.0054</t>
+  </si>
+  <si>
+    <t>0.6840,0.0196,0.2029,0.1118</t>
+  </si>
+  <si>
+    <t>0.9914,0.0029,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.9930,0.0056,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9913,0.0080,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9913,0.0032,0.0022,0.0026</t>
+  </si>
+  <si>
+    <t>0.9827,0.0167,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9816,0.0084,0.0021,0.0044</t>
+  </si>
+  <si>
+    <t>0.9858,0.0120,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.0058,0.0348,0.9766,0.0027</t>
+  </si>
+  <si>
+    <t>0.0033,0.3214,0.9736,0.0017</t>
+  </si>
+  <si>
+    <t>0.0178,0.2081,0.9422,0.0039</t>
+  </si>
+  <si>
+    <t>0.0140,0.0193,0.9622,0.0076</t>
+  </si>
+  <si>
+    <t>0.0050,0.0016,0.9940,0.0007</t>
+  </si>
+  <si>
+    <t>0.0215,0.1446,0.5342,0.5797</t>
+  </si>
+  <si>
+    <t>0.3436,0.0306,0.6651,0.0162</t>
+  </si>
+  <si>
+    <t>0.2564,0.0674,0.6347,0.1154</t>
+  </si>
+  <si>
+    <t>0.8395,0.0010,0.0136,0.1219</t>
+  </si>
+  <si>
+    <t>0.0483,0.0073,0.0201,0.9585</t>
+  </si>
+  <si>
+    <t>0.0985,0.0112,0.0029,0.9480</t>
+  </si>
+  <si>
+    <t>0.0017,0.0003,0.0022,0.9982</t>
+  </si>
+  <si>
+    <t>0.0017,0.0006,0.0017,0.9983</t>
+  </si>
+  <si>
+    <t>0.8198,0.0283,0.0220,0.1314</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1984,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,10 +3398,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4126,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4350,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
